--- a/data/trans_orig/P32-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2007</t>
+          <t>Población según si han pensado que deberían beber menos en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278769</t>
+          <t>278787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288828</t>
+          <t>288865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122786</t>
+          <t>122103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>405049</t>
+          <t>405166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415365</t>
+          <t>415960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213040</t>
+          <t>212975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222124</t>
+          <t>222150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146700</t>
+          <t>146948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365029</t>
+          <t>365068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>374920</t>
+          <t>374993</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318490</t>
+          <t>319837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>332870</t>
+          <t>333195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56045</t>
+          <t>55518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>379452</t>
+          <t>378926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>393899</t>
+          <t>393604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33957</t>
+          <t>31918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>34209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635582</t>
+          <t>637621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>656086</t>
+          <t>656753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185162</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>827719</t>
+          <t>828656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>848484</t>
+          <t>848091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20630</t>
+          <t>20609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203016</t>
+          <t>202332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214192</t>
+          <t>214243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127342</t>
+          <t>127610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138407</t>
+          <t>138408</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335831</t>
+          <t>335852</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351401</t>
+          <t>350785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126991</t>
+          <t>128372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136978</t>
+          <t>136946</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212438</t>
+          <t>212448</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343325</t>
+          <t>343781</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353857</t>
+          <t>353868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>39490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67172</t>
+          <t>67595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48257</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81390</t>
+          <t>82514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1809736</t>
+          <t>1809313</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1838796</t>
+          <t>1837418</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>871892</t>
+          <t>871725</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>887622</t>
+          <t>887473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2690100</t>
+          <t>2688976</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2723233</t>
+          <t>2721347</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2012</t>
+          <t>Población según si han pensado que deberían beber menos en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266603</t>
+          <t>265960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284263</t>
+          <t>284205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135793</t>
+          <t>135220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147939</t>
+          <t>147955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>409297</t>
+          <t>407974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>429995</t>
+          <t>429800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32516</t>
+          <t>31285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227883</t>
+          <t>227879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246128</t>
+          <t>245702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129777</t>
+          <t>130270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141380</t>
+          <t>141356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363350</t>
+          <t>364581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>384710</t>
+          <t>384430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>32586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36943</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>354313</t>
+          <t>355634</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>374621</t>
+          <t>374495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73588</t>
+          <t>73170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>430825</t>
+          <t>431554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452013</t>
+          <t>452261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36608</t>
+          <t>36192</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63956</t>
+          <t>65902</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39535</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67476</t>
+          <t>67717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596983</t>
+          <t>595037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>624331</t>
+          <t>624747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223064</t>
+          <t>222913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230246</t>
+          <t>230236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>824678</t>
+          <t>824437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>852619</t>
+          <t>853504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>279930</t>
+          <t>280665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>295081</t>
+          <t>295385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174150</t>
+          <t>173714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182990</t>
+          <t>183028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>458502</t>
+          <t>459417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>476741</t>
+          <t>476619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29263</t>
+          <t>30446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35212</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110319</t>
+          <t>109136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126722</t>
+          <t>127268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254225</t>
+          <t>253705</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262316</t>
+          <t>262339</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367669</t>
+          <t>369046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>386763</t>
+          <t>387781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115388</t>
+          <t>113789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163330</t>
+          <t>162917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35439</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>135166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187917</t>
+          <t>187661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1876350</t>
+          <t>1876763</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1924292</t>
+          <t>1925891</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1014345</t>
+          <t>1015292</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1035635</t>
+          <t>1035517</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2901546</t>
+          <t>2901802</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2953413</t>
+          <t>2954297</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2016</t>
+          <t>Población según si han pensado que deberían beber menos en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>36599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260729</t>
+          <t>259799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278341</t>
+          <t>278501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138172</t>
+          <t>139649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151027</t>
+          <t>151159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406941</t>
+          <t>406119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>427114</t>
+          <t>426862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>219713</t>
+          <t>220265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>232916</t>
+          <t>233134</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176037</t>
+          <t>175010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187394</t>
+          <t>187397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401051</t>
+          <t>400801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417953</t>
+          <t>418078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19752</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>24279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313484</t>
+          <t>312660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327554</t>
+          <t>326787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>47965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55578</t>
+          <t>55532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>364516</t>
+          <t>365490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381138</t>
+          <t>381263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47699</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56442</t>
+          <t>55533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609017</t>
+          <t>608978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>633473</t>
+          <t>633011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282534</t>
+          <t>283216</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293570</t>
+          <t>293731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>896937</t>
+          <t>897846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>924291</t>
+          <t>923601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>28333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287943</t>
+          <t>287205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>305465</t>
+          <t>305736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183539</t>
+          <t>183140</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475361</t>
+          <t>475828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>494229</t>
+          <t>493859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23498</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37978</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137435</t>
+          <t>138378</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>153657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236219</t>
+          <t>236671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250048</t>
+          <t>250300</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>378719</t>
+          <t>379901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>400214</t>
+          <t>400663</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87095</t>
+          <t>84611</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127649</t>
+          <t>128871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52214</t>
+          <t>50746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118184</t>
+          <t>120108</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167296</t>
+          <t>169546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1866563</t>
+          <t>1865341</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1907117</t>
+          <t>1909601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1091159</t>
+          <t>1092627</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1116825</t>
+          <t>1117310</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2970289</t>
+          <t>2968039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3019401</t>
+          <t>3017477</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2023</t>
+          <t>Población según si han pensado que deberían beber menos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25569</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>13909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256987</t>
+          <t>257006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272947</t>
+          <t>273580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151378</t>
+          <t>151504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160825</t>
+          <t>160705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>412422</t>
+          <t>413863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>431772</t>
+          <t>431391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9851</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198131</t>
+          <t>198295</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209441</t>
+          <t>209565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123457</t>
+          <t>123271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>131087</t>
+          <t>131225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>326227</t>
+          <t>325694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339003</t>
+          <t>339134</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>22510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189152</t>
+          <t>188785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203014</t>
+          <t>203687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36291</t>
+          <t>36532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228638</t>
+          <t>227874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243072</t>
+          <t>243085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>46235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54178</t>
+          <t>53232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>463553</t>
+          <t>463541</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490371</t>
+          <t>490690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>402904</t>
+          <t>402751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>413789</t>
+          <t>413878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>869640</t>
+          <t>870586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>908024</t>
+          <t>908219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33409</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203368</t>
+          <t>202265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>220372</t>
+          <t>220289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122262</t>
+          <t>121850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128912</t>
+          <t>129050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329549</t>
+          <t>329142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>347311</t>
+          <t>347334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68875</t>
+          <t>69910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93107</t>
+          <t>93080</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189649</t>
+          <t>187704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>213866</t>
+          <t>212781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76033</t>
+          <t>77471</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118659</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33533</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89023</t>
+          <t>86052</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145730</t>
+          <t>144712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1424627</t>
+          <t>1421742</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1467253</t>
+          <t>1465815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>969419</t>
+          <t>970524</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>992947</t>
+          <t>993264</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2400509</t>
+          <t>2401527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2457216</t>
+          <t>2460187</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278787</t>
+          <t>277638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288865</t>
+          <t>288838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122103</t>
+          <t>122948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>405166</t>
+          <t>405132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415960</t>
+          <t>415954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212975</t>
+          <t>212751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222150</t>
+          <t>222144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146948</t>
+          <t>147470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365068</t>
+          <t>364968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>374993</t>
+          <t>375059</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319837</t>
+          <t>318836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>333195</t>
+          <t>332405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55518</t>
+          <t>55609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378926</t>
+          <t>378376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>393604</t>
+          <t>393975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31918</t>
+          <t>31468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637621</t>
+          <t>638071</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>656753</t>
+          <t>656847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184760</t>
+          <t>184576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>828656</t>
+          <t>829322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>848091</t>
+          <t>848511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20609</t>
+          <t>21225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202332</t>
+          <t>202634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214243</t>
+          <t>214094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127610</t>
+          <t>128061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138408</t>
+          <t>138410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335852</t>
+          <t>335236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>350785</t>
+          <t>350182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128372</t>
+          <t>127436</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136946</t>
+          <t>137523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212448</t>
+          <t>212467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343781</t>
+          <t>344345</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353868</t>
+          <t>353897</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>38195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67595</t>
+          <t>67278</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50143</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82514</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1809313</t>
+          <t>1809630</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1837418</t>
+          <t>1838713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>871725</t>
+          <t>872331</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>887473</t>
+          <t>887415</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2688976</t>
+          <t>2689488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2721347</t>
+          <t>2721190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>34169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265960</t>
+          <t>265848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284205</t>
+          <t>283310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135220</t>
+          <t>136302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147955</t>
+          <t>147943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>407974</t>
+          <t>408436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>429800</t>
+          <t>429978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31285</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227879</t>
+          <t>226928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245702</t>
+          <t>245938</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130270</t>
+          <t>130451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141356</t>
+          <t>140728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>364581</t>
+          <t>363109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>384430</t>
+          <t>384436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13291</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36214</t>
+          <t>38348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>355634</t>
+          <t>354605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>374495</t>
+          <t>374929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73170</t>
+          <t>73658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>431554</t>
+          <t>429420</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452261</t>
+          <t>451678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>65026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38650</t>
+          <t>39604</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67717</t>
+          <t>71147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>595037</t>
+          <t>595913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>624747</t>
+          <t>623241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222913</t>
+          <t>223277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230236</t>
+          <t>230245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>824437</t>
+          <t>821007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>853504</t>
+          <t>852550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>25109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>29725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280665</t>
+          <t>279012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>295385</t>
+          <t>295115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173714</t>
+          <t>174074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183028</t>
+          <t>182995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>459417</t>
+          <t>458464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>476619</t>
+          <t>475862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30446</t>
+          <t>30676</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109136</t>
+          <t>108906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127268</t>
+          <t>126601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253705</t>
+          <t>253621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262339</t>
+          <t>262293</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>369046</t>
+          <t>368396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>387781</t>
+          <t>387860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113789</t>
+          <t>114853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162917</t>
+          <t>164126</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34492</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135166</t>
+          <t>137634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187661</t>
+          <t>187683</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1876763</t>
+          <t>1875554</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1925891</t>
+          <t>1924827</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1015292</t>
+          <t>1014780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1035517</t>
+          <t>1035861</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2901802</t>
+          <t>2901780</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2954297</t>
+          <t>2951829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14292</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36599</t>
+          <t>36831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259799</t>
+          <t>261701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278501</t>
+          <t>278945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139649</t>
+          <t>139789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151159</t>
+          <t>151485</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406119</t>
+          <t>405887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>426862</t>
+          <t>427225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>27493</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>220265</t>
+          <t>219428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>233134</t>
+          <t>233196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175010</t>
+          <t>175778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187397</t>
+          <t>187363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>400801</t>
+          <t>402066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>418078</t>
+          <t>418402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>25677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312660</t>
+          <t>312044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>326787</t>
+          <t>326910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47965</t>
+          <t>47196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55532</t>
+          <t>55527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>365490</t>
+          <t>364092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381263</t>
+          <t>381396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>22606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55533</t>
+          <t>54960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>608978</t>
+          <t>608717</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>633011</t>
+          <t>634110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283216</t>
+          <t>283352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293731</t>
+          <t>293650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>897846</t>
+          <t>898419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>923601</t>
+          <t>925205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28333</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29634</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287205</t>
+          <t>287647</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>305736</t>
+          <t>305405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183140</t>
+          <t>182852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475828</t>
+          <t>474951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>493859</t>
+          <t>494107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16034</t>
+          <t>15829</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>35732</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138378</t>
+          <t>137743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153657</t>
+          <t>153510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236671</t>
+          <t>236366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250300</t>
+          <t>250139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>379901</t>
+          <t>380965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>400663</t>
+          <t>400868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84611</t>
+          <t>85209</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128871</t>
+          <t>127459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>26561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50746</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120108</t>
+          <t>118652</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169546</t>
+          <t>167685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1865341</t>
+          <t>1866753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1909601</t>
+          <t>1909003</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1092627</t>
+          <t>1092449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1117310</t>
+          <t>1116812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2968039</t>
+          <t>2969900</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3017477</t>
+          <t>3018933</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21338</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>35359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>266368</t>
+          <t>284899</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257006</t>
+          <t>274982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273580</t>
+          <t>292666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>157594</t>
+          <t>169255</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151504</t>
+          <t>162098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160705</t>
+          <t>172745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>423962</t>
+          <t>454154</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413863</t>
+          <t>443591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>431391</t>
+          <t>462914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>282556</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>282556</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>282556</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>445300</t>
+          <t>478950</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>445300</t>
+          <t>478950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>445300</t>
+          <t>478950</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>205200</t>
+          <t>215737</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198295</t>
+          <t>207762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209565</t>
+          <t>220156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>128451</t>
+          <t>138645</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123271</t>
+          <t>132876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>131225</t>
+          <t>142171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>333652</t>
+          <t>354382</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>325694</t>
+          <t>345919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339134</t>
+          <t>360894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>145015</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>145015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>145015</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>369706</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>369706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>369706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22510</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>806</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>197466</t>
+          <t>212275</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188785</t>
+          <t>201867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203687</t>
+          <t>218961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,27 +9467,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39611</t>
+          <t>45759</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36532</t>
+          <t>42396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>237078</t>
+          <t>258034</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>227874</t>
+          <t>247990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243085</t>
+          <t>264712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30506</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19086</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>47642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>37666</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>54599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>479270</t>
+          <t>510891</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>463541</t>
+          <t>495249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490690</t>
+          <t>521545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>410552</t>
+          <t>224069</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>402751</t>
+          <t>215381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>413878</t>
+          <t>227969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>889822</t>
+          <t>734960</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>870586</t>
+          <t>718027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>908219</t>
+          <t>747111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>414042</t>
+          <t>229735</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>414042</t>
+          <t>229735</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>414042</t>
+          <t>229735</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>923818</t>
+          <t>772626</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>923818</t>
+          <t>772626</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>923818</t>
+          <t>772626</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29570</t>
+          <t>34596</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>23560</t>
+          <t>28258</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>212971</t>
+          <t>234533</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202265</t>
+          <t>223181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>220289</t>
+          <t>243523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126427</t>
+          <t>148234</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121850</t>
+          <t>143027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>150797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>339398</t>
+          <t>382767</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329142</t>
+          <t>371373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>347334</t>
+          <t>391699</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>231835</t>
+          <t>257777</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231835</t>
+          <t>257777</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231835</t>
+          <t>257777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362958</t>
+          <t>411025</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362958</t>
+          <t>411025</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362958</t>
+          <t>411025</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>86094</t>
+          <t>77898</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69910</t>
+          <t>66175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93080</t>
+          <t>84283</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>124247</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>114842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>205269</t>
+          <t>202146</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>187704</t>
+          <t>189521</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>212781</t>
+          <t>210016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>95917</t>
+          <t>106612</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77471</t>
+          <t>87446</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121544</t>
+          <t>132089</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>37546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>117059</t>
+          <t>132850</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144712</t>
+          <t>159679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1447369</t>
+          <t>1536234</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1421742</t>
+          <t>1510757</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1465815</t>
+          <t>1555400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>981810</t>
+          <t>850209</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>970524</t>
+          <t>838901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>993264</t>
+          <t>858875</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2429180</t>
+          <t>2386443</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2401527</t>
+          <t>2359614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2460187</t>
+          <t>2409183</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1543286</t>
+          <t>1642846</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1543286</t>
+          <t>1642846</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1543286</t>
+          <t>1642846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1002952</t>
+          <t>876447</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1002952</t>
+          <t>876447</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1002952</t>
+          <t>876447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2546239</t>
+          <t>2519293</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2546239</t>
+          <t>2519293</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2546239</t>
+          <t>2519293</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
